--- a/erp-server/erp-server-file/src/main/resources/excel/wms/virtualHisInventoryAge.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/wms/virtualHisInventoryAge.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t>SKU</t>
   </si>
@@ -46,9 +46,6 @@
     <t>虚拟仓名称</t>
   </si>
   <si>
-    <t>统计日期</t>
-  </si>
-  <si>
     <t>平均库龄（天）</t>
   </si>
   <si>
@@ -65,9 +62,6 @@
   </si>
   <si>
     <t>{.virtualWarehouseName}</t>
-  </si>
-  <si>
-    <t>{.date}</t>
   </si>
   <si>
     <t>{.avgInventoryAgeDays}</t>
@@ -1001,19 +995,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1" outlineLevelCol="6"/>
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="15.875" customWidth="1"/>
     <col min="2" max="2" width="17.5" customWidth="1"/>
     <col min="3" max="3" width="19.75" customWidth="1"/>
     <col min="4" max="4" width="19" customWidth="1"/>
     <col min="5" max="5" width="20.75" customWidth="1"/>
-    <col min="6" max="6" width="16.625" customWidth="1"/>
-    <col min="7" max="7" width="18" customWidth="1"/>
+    <col min="6" max="6" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:6">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1032,31 +1025,25 @@
       <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" spans="1:7">
-      <c r="A2" t="s">
+      <c r="B2" t="s">
         <v>7</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>8</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>9</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>10</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>11</v>
-      </c>
-      <c r="F2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G2" t="s">
-        <v>13</v>
       </c>
     </row>
   </sheetData>

--- a/erp-server/erp-server-file/src/main/resources/excel/wms/virtualHisInventoryAge.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/wms/virtualHisInventoryAge.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
   <si>
     <t>SKU</t>
   </si>
@@ -46,6 +46,9 @@
     <t>虚拟仓名称</t>
   </si>
   <si>
+    <t>统计日期</t>
+  </si>
+  <si>
     <t>平均库龄（天）</t>
   </si>
   <si>
@@ -62,6 +65,9 @@
   </si>
   <si>
     <t>{.virtualWarehouseName}</t>
+  </si>
+  <si>
+    <t>{.date}</t>
   </si>
   <si>
     <t>{.avgInventoryAgeDays}</t>
@@ -995,18 +1001,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1" outlineLevelCol="5"/>
+  <dimension ref="A1:G2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="15.875" customWidth="1"/>
     <col min="2" max="2" width="17.5" customWidth="1"/>
     <col min="3" max="3" width="19.75" customWidth="1"/>
     <col min="4" max="4" width="19" customWidth="1"/>
-    <col min="5" max="5" width="20.75" customWidth="1"/>
-    <col min="6" max="6" width="18" customWidth="1"/>
+    <col min="5" max="6" width="20.75" customWidth="1"/>
+    <col min="7" max="7" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:7">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1025,25 +1031,31 @@
       <c r="F1" t="s">
         <v>5</v>
       </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:7">
       <c r="A2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F2" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="G2" t="s">
+        <v>13</v>
       </c>
     </row>
   </sheetData>
